--- a/sample_templates/期初在产品.xlsx
+++ b/sample_templates/期初在产品.xlsx
@@ -460,7 +460,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I10"/>
+  <dimension ref="A1:J10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -494,42 +494,47 @@
           <t>工单号</t>
         </is>
       </c>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>数量</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
         <is>
           <t>材料成本</t>
         </is>
       </c>
-      <c r="C3" s="3" t="inlineStr">
+      <c r="D3" s="3" t="inlineStr">
         <is>
           <t>水电</t>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr">
+      <c r="E3" s="3" t="inlineStr">
         <is>
           <t>蒸汽</t>
         </is>
       </c>
-      <c r="E3" s="3" t="inlineStr">
+      <c r="F3" s="3" t="inlineStr">
         <is>
           <t>天然气</t>
         </is>
       </c>
-      <c r="F3" s="3" t="inlineStr">
+      <c r="G3" s="3" t="inlineStr">
         <is>
           <t>折旧</t>
         </is>
       </c>
-      <c r="G3" s="3" t="inlineStr">
+      <c r="H3" s="3" t="inlineStr">
         <is>
           <t>机物料</t>
         </is>
       </c>
-      <c r="H3" s="3" t="inlineStr">
+      <c r="I3" s="3" t="inlineStr">
         <is>
           <t>染料助剂</t>
         </is>
       </c>
-      <c r="I3" s="3" t="inlineStr">
+      <c r="J3" s="3" t="inlineStr">
         <is>
           <t>工资</t>
         </is>
@@ -541,42 +546,47 @@
           <t>示例-RZ-WIP1</t>
         </is>
       </c>
-      <c r="B4" s="5" t="inlineStr">
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>4800</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
         <is>
           <t>1000.00</t>
         </is>
       </c>
-      <c r="C4" s="5" t="inlineStr">
+      <c r="D4" s="5" t="inlineStr">
         <is>
           <t>50.00</t>
         </is>
       </c>
-      <c r="D4" s="5" t="inlineStr">
+      <c r="E4" s="5" t="inlineStr">
         <is>
           <t>30.00</t>
         </is>
       </c>
-      <c r="E4" s="5" t="inlineStr">
+      <c r="F4" s="5" t="inlineStr">
         <is>
           <t>20.00</t>
         </is>
       </c>
-      <c r="F4" s="5" t="inlineStr">
+      <c r="G4" s="5" t="inlineStr">
         <is>
           <t>40.00</t>
         </is>
       </c>
-      <c r="G4" s="5" t="inlineStr">
+      <c r="H4" s="5" t="inlineStr">
         <is>
           <t>10.00</t>
         </is>
       </c>
-      <c r="H4" s="5" t="inlineStr">
+      <c r="I4" s="5" t="inlineStr">
         <is>
           <t>60.00</t>
         </is>
       </c>
-      <c r="I4" s="5" t="inlineStr">
+      <c r="J4" s="5" t="inlineStr">
         <is>
           <t>80.00</t>
         </is>
@@ -588,102 +598,57 @@
           <t>示例-RZ-WIP2</t>
         </is>
       </c>
-      <c r="B5" s="5" t="inlineStr">
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>1200</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
         <is>
           <t>800.00</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="D5" s="5" t="inlineStr">
         <is>
           <t>40.00</t>
         </is>
       </c>
-      <c r="D5" s="5" t="inlineStr">
+      <c r="E5" s="5" t="inlineStr">
         <is>
           <t>25.00</t>
         </is>
       </c>
-      <c r="E5" s="5" t="inlineStr">
+      <c r="F5" s="5" t="inlineStr">
         <is>
           <t>15.00</t>
         </is>
       </c>
-      <c r="F5" s="5" t="inlineStr">
+      <c r="G5" s="5" t="inlineStr">
         <is>
           <t>30.00</t>
         </is>
       </c>
-      <c r="G5" s="5" t="inlineStr">
+      <c r="H5" s="5" t="inlineStr">
         <is>
           <t>8.00</t>
         </is>
       </c>
-      <c r="H5" s="5" t="inlineStr">
+      <c r="I5" s="5" t="inlineStr">
         <is>
           <t>50.00</t>
         </is>
       </c>
-      <c r="I5" s="5" t="inlineStr">
+      <c r="J5" s="5" t="inlineStr">
         <is>
           <t>70.00</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr"/>
-      <c r="B6" t="inlineStr"/>
-      <c r="C6" t="inlineStr"/>
-      <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr"/>
-      <c r="B7" t="inlineStr"/>
-      <c r="C7" t="inlineStr"/>
-      <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr"/>
-      <c r="B8" t="inlineStr"/>
-      <c r="C8" t="inlineStr"/>
-      <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr"/>
-      <c r="B9" t="inlineStr"/>
-      <c r="C9" t="inlineStr"/>
-      <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr"/>
-      <c r="B10" t="inlineStr"/>
-      <c r="C10" t="inlineStr"/>
-      <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr"/>
-    </row>
+    <row r="6"/>
+    <row r="7"/>
+    <row r="8"/>
+    <row r="9"/>
+    <row r="10"/>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:I1"/>
@@ -699,7 +664,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I10"/>
+  <dimension ref="A1:J10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -733,42 +698,47 @@
           <t>工单号</t>
         </is>
       </c>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>数量</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
         <is>
           <t>材料成本</t>
         </is>
       </c>
-      <c r="C3" s="3" t="inlineStr">
+      <c r="D3" s="3" t="inlineStr">
         <is>
           <t>水电</t>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr">
+      <c r="E3" s="3" t="inlineStr">
         <is>
           <t>蒸汽</t>
         </is>
       </c>
-      <c r="E3" s="3" t="inlineStr">
+      <c r="F3" s="3" t="inlineStr">
         <is>
           <t>天然气</t>
         </is>
       </c>
-      <c r="F3" s="3" t="inlineStr">
+      <c r="G3" s="3" t="inlineStr">
         <is>
           <t>折旧</t>
         </is>
       </c>
-      <c r="G3" s="3" t="inlineStr">
+      <c r="H3" s="3" t="inlineStr">
         <is>
           <t>机物料</t>
         </is>
       </c>
-      <c r="H3" s="3" t="inlineStr">
+      <c r="I3" s="3" t="inlineStr">
         <is>
           <t>染料助剂</t>
         </is>
       </c>
-      <c r="I3" s="3" t="inlineStr">
+      <c r="J3" s="3" t="inlineStr">
         <is>
           <t>工资</t>
         </is>
@@ -780,34 +750,39 @@
           <t>示例-TF-WIP1</t>
         </is>
       </c>
-      <c r="B4" s="5" t="inlineStr">
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>4800</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
         <is>
           <t>2000.00</t>
         </is>
       </c>
-      <c r="C4" s="5" t="inlineStr">
+      <c r="D4" s="5" t="inlineStr">
         <is>
           <t>80.00</t>
         </is>
       </c>
-      <c r="D4" s="5" t="inlineStr">
+      <c r="E4" s="5" t="inlineStr">
         <is>
           <t>60.00</t>
         </is>
       </c>
-      <c r="E4" s="5" t="inlineStr"/>
-      <c r="F4" s="5" t="inlineStr">
+      <c r="F4" s="5" t="inlineStr"/>
+      <c r="G4" s="5" t="inlineStr">
         <is>
           <t>50.00</t>
         </is>
       </c>
-      <c r="G4" s="5" t="inlineStr">
+      <c r="H4" s="5" t="inlineStr">
         <is>
           <t>20.00</t>
         </is>
       </c>
-      <c r="H4" s="5" t="inlineStr"/>
-      <c r="I4" s="5" t="inlineStr">
+      <c r="I4" s="5" t="inlineStr"/>
+      <c r="J4" s="5" t="inlineStr">
         <is>
           <t>120.00</t>
         </is>
@@ -819,94 +794,49 @@
           <t>示例-TF-WIP2</t>
         </is>
       </c>
-      <c r="B5" s="5" t="inlineStr">
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>1200</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
         <is>
           <t>1500.00</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="D5" s="5" t="inlineStr">
         <is>
           <t>60.00</t>
         </is>
       </c>
-      <c r="D5" s="5" t="inlineStr">
+      <c r="E5" s="5" t="inlineStr">
         <is>
           <t>45.00</t>
         </is>
       </c>
-      <c r="E5" s="5" t="inlineStr"/>
-      <c r="F5" s="5" t="inlineStr">
+      <c r="F5" s="5" t="inlineStr"/>
+      <c r="G5" s="5" t="inlineStr">
         <is>
           <t>35.00</t>
         </is>
       </c>
-      <c r="G5" s="5" t="inlineStr">
+      <c r="H5" s="5" t="inlineStr">
         <is>
           <t>15.00</t>
         </is>
       </c>
-      <c r="H5" s="5" t="inlineStr"/>
-      <c r="I5" s="5" t="inlineStr">
+      <c r="I5" s="5" t="inlineStr"/>
+      <c r="J5" s="5" t="inlineStr">
         <is>
           <t>100.00</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr"/>
-      <c r="B6" t="inlineStr"/>
-      <c r="C6" t="inlineStr"/>
-      <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr"/>
-      <c r="B7" t="inlineStr"/>
-      <c r="C7" t="inlineStr"/>
-      <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr"/>
-      <c r="B8" t="inlineStr"/>
-      <c r="C8" t="inlineStr"/>
-      <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr"/>
-      <c r="B9" t="inlineStr"/>
-      <c r="C9" t="inlineStr"/>
-      <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr"/>
-      <c r="B10" t="inlineStr"/>
-      <c r="C10" t="inlineStr"/>
-      <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr"/>
-    </row>
+    <row r="6"/>
+    <row r="7"/>
+    <row r="8"/>
+    <row r="9"/>
+    <row r="10"/>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:I1"/>
@@ -922,7 +852,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I10"/>
+  <dimension ref="A1:J10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -956,42 +886,47 @@
           <t>工单号</t>
         </is>
       </c>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>数量</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
         <is>
           <t>材料成本</t>
         </is>
       </c>
-      <c r="C3" s="3" t="inlineStr">
+      <c r="D3" s="3" t="inlineStr">
         <is>
           <t>水电</t>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr">
+      <c r="E3" s="3" t="inlineStr">
         <is>
           <t>蒸汽</t>
         </is>
       </c>
-      <c r="E3" s="3" t="inlineStr">
+      <c r="F3" s="3" t="inlineStr">
         <is>
           <t>天然气</t>
         </is>
       </c>
-      <c r="F3" s="3" t="inlineStr">
+      <c r="G3" s="3" t="inlineStr">
         <is>
           <t>折旧</t>
         </is>
       </c>
-      <c r="G3" s="3" t="inlineStr">
+      <c r="H3" s="3" t="inlineStr">
         <is>
           <t>机物料</t>
         </is>
       </c>
-      <c r="H3" s="3" t="inlineStr">
+      <c r="I3" s="3" t="inlineStr">
         <is>
           <t>染料助剂</t>
         </is>
       </c>
-      <c r="I3" s="3" t="inlineStr">
+      <c r="J3" s="3" t="inlineStr">
         <is>
           <t>工资</t>
         </is>
@@ -1003,34 +938,39 @@
           <t>示例-BF-WIP1</t>
         </is>
       </c>
-      <c r="B4" s="5" t="inlineStr">
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>4800</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
         <is>
           <t>500.00</t>
         </is>
       </c>
-      <c r="C4" s="5" t="inlineStr">
+      <c r="D4" s="5" t="inlineStr">
         <is>
           <t>20.00</t>
         </is>
       </c>
-      <c r="D4" s="5" t="inlineStr">
+      <c r="E4" s="5" t="inlineStr">
         <is>
           <t>10.00</t>
         </is>
       </c>
-      <c r="E4" s="5" t="inlineStr"/>
-      <c r="F4" s="5" t="inlineStr">
+      <c r="F4" s="5" t="inlineStr"/>
+      <c r="G4" s="5" t="inlineStr">
         <is>
           <t>15.00</t>
         </is>
       </c>
-      <c r="G4" s="5" t="inlineStr">
+      <c r="H4" s="5" t="inlineStr">
         <is>
           <t>5.00</t>
         </is>
       </c>
-      <c r="H4" s="5" t="inlineStr"/>
-      <c r="I4" s="5" t="inlineStr">
+      <c r="I4" s="5" t="inlineStr"/>
+      <c r="J4" s="5" t="inlineStr">
         <is>
           <t>40.00</t>
         </is>
@@ -1042,94 +982,49 @@
           <t>示例-BF-WIP2</t>
         </is>
       </c>
-      <c r="B5" s="5" t="inlineStr">
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>1200</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
         <is>
           <t>300.00</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="D5" s="5" t="inlineStr">
         <is>
           <t>12.00</t>
         </is>
       </c>
-      <c r="D5" s="5" t="inlineStr">
+      <c r="E5" s="5" t="inlineStr">
         <is>
           <t>8.00</t>
         </is>
       </c>
-      <c r="E5" s="5" t="inlineStr"/>
-      <c r="F5" s="5" t="inlineStr">
+      <c r="F5" s="5" t="inlineStr"/>
+      <c r="G5" s="5" t="inlineStr">
         <is>
           <t>10.00</t>
         </is>
       </c>
-      <c r="G5" s="5" t="inlineStr">
+      <c r="H5" s="5" t="inlineStr">
         <is>
           <t>3.00</t>
         </is>
       </c>
-      <c r="H5" s="5" t="inlineStr"/>
-      <c r="I5" s="5" t="inlineStr">
+      <c r="I5" s="5" t="inlineStr"/>
+      <c r="J5" s="5" t="inlineStr">
         <is>
           <t>30.00</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr"/>
-      <c r="B6" t="inlineStr"/>
-      <c r="C6" t="inlineStr"/>
-      <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr"/>
-      <c r="B7" t="inlineStr"/>
-      <c r="C7" t="inlineStr"/>
-      <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr"/>
-      <c r="B8" t="inlineStr"/>
-      <c r="C8" t="inlineStr"/>
-      <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr"/>
-      <c r="B9" t="inlineStr"/>
-      <c r="C9" t="inlineStr"/>
-      <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr"/>
-      <c r="B10" t="inlineStr"/>
-      <c r="C10" t="inlineStr"/>
-      <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr"/>
-    </row>
+    <row r="6"/>
+    <row r="7"/>
+    <row r="8"/>
+    <row r="9"/>
+    <row r="10"/>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:I1"/>
@@ -1145,7 +1040,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I10"/>
+  <dimension ref="A1:J10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -1179,42 +1074,47 @@
           <t>工单号</t>
         </is>
       </c>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>数量</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
         <is>
           <t>材料成本</t>
         </is>
       </c>
-      <c r="C3" s="3" t="inlineStr">
+      <c r="D3" s="3" t="inlineStr">
         <is>
           <t>水电</t>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr">
+      <c r="E3" s="3" t="inlineStr">
         <is>
           <t>蒸汽</t>
         </is>
       </c>
-      <c r="E3" s="3" t="inlineStr">
+      <c r="F3" s="3" t="inlineStr">
         <is>
           <t>天然气</t>
         </is>
       </c>
-      <c r="F3" s="3" t="inlineStr">
+      <c r="G3" s="3" t="inlineStr">
         <is>
           <t>折旧</t>
         </is>
       </c>
-      <c r="G3" s="3" t="inlineStr">
+      <c r="H3" s="3" t="inlineStr">
         <is>
           <t>机物料</t>
         </is>
       </c>
-      <c r="H3" s="3" t="inlineStr">
+      <c r="I3" s="3" t="inlineStr">
         <is>
           <t>染料助剂</t>
         </is>
       </c>
-      <c r="I3" s="3" t="inlineStr">
+      <c r="J3" s="3" t="inlineStr">
         <is>
           <t>工资</t>
         </is>
@@ -1226,34 +1126,39 @@
           <t>示例-ZZ-WIP1</t>
         </is>
       </c>
-      <c r="B4" s="5" t="inlineStr">
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>4800</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
         <is>
           <t>600.00</t>
         </is>
       </c>
-      <c r="C4" s="5" t="inlineStr">
+      <c r="D4" s="5" t="inlineStr">
         <is>
           <t>25.00</t>
         </is>
       </c>
-      <c r="D4" s="5" t="inlineStr">
+      <c r="E4" s="5" t="inlineStr">
         <is>
           <t>12.00</t>
         </is>
       </c>
-      <c r="E4" s="5" t="inlineStr"/>
-      <c r="F4" s="5" t="inlineStr">
+      <c r="F4" s="5" t="inlineStr"/>
+      <c r="G4" s="5" t="inlineStr">
         <is>
           <t>18.00</t>
         </is>
       </c>
-      <c r="G4" s="5" t="inlineStr">
+      <c r="H4" s="5" t="inlineStr">
         <is>
           <t>6.00</t>
         </is>
       </c>
-      <c r="H4" s="5" t="inlineStr"/>
-      <c r="I4" s="5" t="inlineStr">
+      <c r="I4" s="5" t="inlineStr"/>
+      <c r="J4" s="5" t="inlineStr">
         <is>
           <t>45.00</t>
         </is>
@@ -1265,94 +1170,49 @@
           <t>示例-ZZ-WIP2</t>
         </is>
       </c>
-      <c r="B5" s="5" t="inlineStr">
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>1200</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
         <is>
           <t>450.00</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="D5" s="5" t="inlineStr">
         <is>
           <t>18.00</t>
         </is>
       </c>
-      <c r="D5" s="5" t="inlineStr">
+      <c r="E5" s="5" t="inlineStr">
         <is>
           <t>9.00</t>
         </is>
       </c>
-      <c r="E5" s="5" t="inlineStr"/>
-      <c r="F5" s="5" t="inlineStr">
+      <c r="F5" s="5" t="inlineStr"/>
+      <c r="G5" s="5" t="inlineStr">
         <is>
           <t>12.00</t>
         </is>
       </c>
-      <c r="G5" s="5" t="inlineStr">
+      <c r="H5" s="5" t="inlineStr">
         <is>
           <t>4.00</t>
         </is>
       </c>
-      <c r="H5" s="5" t="inlineStr"/>
-      <c r="I5" s="5" t="inlineStr">
+      <c r="I5" s="5" t="inlineStr"/>
+      <c r="J5" s="5" t="inlineStr">
         <is>
           <t>35.00</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr"/>
-      <c r="B6" t="inlineStr"/>
-      <c r="C6" t="inlineStr"/>
-      <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr"/>
-      <c r="B7" t="inlineStr"/>
-      <c r="C7" t="inlineStr"/>
-      <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr"/>
-      <c r="B8" t="inlineStr"/>
-      <c r="C8" t="inlineStr"/>
-      <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr"/>
-      <c r="B9" t="inlineStr"/>
-      <c r="C9" t="inlineStr"/>
-      <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr"/>
-      <c r="B10" t="inlineStr"/>
-      <c r="C10" t="inlineStr"/>
-      <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr"/>
-    </row>
+    <row r="6"/>
+    <row r="7"/>
+    <row r="8"/>
+    <row r="9"/>
+    <row r="10"/>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:I1"/>
@@ -1368,7 +1228,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I10"/>
+  <dimension ref="A1:J10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -1402,42 +1262,47 @@
           <t>工单号</t>
         </is>
       </c>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>数量</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
         <is>
           <t>材料成本</t>
         </is>
       </c>
-      <c r="C3" s="3" t="inlineStr">
+      <c r="D3" s="3" t="inlineStr">
         <is>
           <t>水电</t>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr">
+      <c r="E3" s="3" t="inlineStr">
         <is>
           <t>蒸汽</t>
         </is>
       </c>
-      <c r="E3" s="3" t="inlineStr">
+      <c r="F3" s="3" t="inlineStr">
         <is>
           <t>天然气</t>
         </is>
       </c>
-      <c r="F3" s="3" t="inlineStr">
+      <c r="G3" s="3" t="inlineStr">
         <is>
           <t>折旧</t>
         </is>
       </c>
-      <c r="G3" s="3" t="inlineStr">
+      <c r="H3" s="3" t="inlineStr">
         <is>
           <t>机物料</t>
         </is>
       </c>
-      <c r="H3" s="3" t="inlineStr">
+      <c r="I3" s="3" t="inlineStr">
         <is>
           <t>染料助剂</t>
         </is>
       </c>
-      <c r="I3" s="3" t="inlineStr">
+      <c r="J3" s="3" t="inlineStr">
         <is>
           <t>工资</t>
         </is>
@@ -1449,34 +1314,39 @@
           <t>示例-JZ-WIP1</t>
         </is>
       </c>
-      <c r="B4" s="5" t="inlineStr">
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>4800</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
         <is>
           <t>900.00</t>
         </is>
       </c>
-      <c r="C4" s="5" t="inlineStr">
+      <c r="D4" s="5" t="inlineStr">
         <is>
           <t>35.00</t>
         </is>
       </c>
-      <c r="D4" s="5" t="inlineStr">
+      <c r="E4" s="5" t="inlineStr">
         <is>
           <t>15.00</t>
         </is>
       </c>
-      <c r="E4" s="5" t="inlineStr"/>
-      <c r="F4" s="5" t="inlineStr">
+      <c r="F4" s="5" t="inlineStr"/>
+      <c r="G4" s="5" t="inlineStr">
         <is>
           <t>25.00</t>
         </is>
       </c>
-      <c r="G4" s="5" t="inlineStr">
+      <c r="H4" s="5" t="inlineStr">
         <is>
           <t>8.00</t>
         </is>
       </c>
-      <c r="H4" s="5" t="inlineStr"/>
-      <c r="I4" s="5" t="inlineStr">
+      <c r="I4" s="5" t="inlineStr"/>
+      <c r="J4" s="5" t="inlineStr">
         <is>
           <t>55.00</t>
         </is>
@@ -1488,94 +1358,49 @@
           <t>示例-JZ-WIP2</t>
         </is>
       </c>
-      <c r="B5" s="5" t="inlineStr">
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>1200</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
         <is>
           <t>700.00</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="D5" s="5" t="inlineStr">
         <is>
           <t>28.00</t>
         </is>
       </c>
-      <c r="D5" s="5" t="inlineStr">
+      <c r="E5" s="5" t="inlineStr">
         <is>
           <t>12.00</t>
         </is>
       </c>
-      <c r="E5" s="5" t="inlineStr"/>
-      <c r="F5" s="5" t="inlineStr">
+      <c r="F5" s="5" t="inlineStr"/>
+      <c r="G5" s="5" t="inlineStr">
         <is>
           <t>20.00</t>
         </is>
       </c>
-      <c r="G5" s="5" t="inlineStr">
+      <c r="H5" s="5" t="inlineStr">
         <is>
           <t>6.00</t>
         </is>
       </c>
-      <c r="H5" s="5" t="inlineStr"/>
-      <c r="I5" s="5" t="inlineStr">
+      <c r="I5" s="5" t="inlineStr"/>
+      <c r="J5" s="5" t="inlineStr">
         <is>
           <t>45.00</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr"/>
-      <c r="B6" t="inlineStr"/>
-      <c r="C6" t="inlineStr"/>
-      <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr"/>
-      <c r="B7" t="inlineStr"/>
-      <c r="C7" t="inlineStr"/>
-      <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr"/>
-      <c r="B8" t="inlineStr"/>
-      <c r="C8" t="inlineStr"/>
-      <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr"/>
-      <c r="B9" t="inlineStr"/>
-      <c r="C9" t="inlineStr"/>
-      <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr"/>
-      <c r="B10" t="inlineStr"/>
-      <c r="C10" t="inlineStr"/>
-      <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr"/>
-    </row>
+    <row r="6"/>
+    <row r="7"/>
+    <row r="8"/>
+    <row r="9"/>
+    <row r="10"/>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:I1"/>
@@ -1591,7 +1416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I10"/>
+  <dimension ref="A1:J10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -1625,42 +1450,47 @@
           <t>工单号</t>
         </is>
       </c>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>数量</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
         <is>
           <t>材料成本</t>
         </is>
       </c>
-      <c r="C3" s="3" t="inlineStr">
+      <c r="D3" s="3" t="inlineStr">
         <is>
           <t>水电</t>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr">
+      <c r="E3" s="3" t="inlineStr">
         <is>
           <t>蒸汽</t>
         </is>
       </c>
-      <c r="E3" s="3" t="inlineStr">
+      <c r="F3" s="3" t="inlineStr">
         <is>
           <t>天然气</t>
         </is>
       </c>
-      <c r="F3" s="3" t="inlineStr">
+      <c r="G3" s="3" t="inlineStr">
         <is>
           <t>折旧</t>
         </is>
       </c>
-      <c r="G3" s="3" t="inlineStr">
+      <c r="H3" s="3" t="inlineStr">
         <is>
           <t>机物料</t>
         </is>
       </c>
-      <c r="H3" s="3" t="inlineStr">
+      <c r="I3" s="3" t="inlineStr">
         <is>
           <t>染料助剂</t>
         </is>
       </c>
-      <c r="I3" s="3" t="inlineStr">
+      <c r="J3" s="3" t="inlineStr">
         <is>
           <t>工资</t>
         </is>
@@ -1672,38 +1502,43 @@
           <t>示例-JP-WIP1</t>
         </is>
       </c>
-      <c r="B4" s="5" t="inlineStr">
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>4800</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
         <is>
           <t>3000.00</t>
         </is>
       </c>
-      <c r="C4" s="5" t="inlineStr">
+      <c r="D4" s="5" t="inlineStr">
         <is>
           <t>100.00</t>
         </is>
       </c>
-      <c r="D4" s="5" t="inlineStr">
+      <c r="E4" s="5" t="inlineStr">
         <is>
           <t>70.00</t>
         </is>
       </c>
-      <c r="E4" s="5" t="inlineStr">
+      <c r="F4" s="5" t="inlineStr">
         <is>
           <t>50.00</t>
         </is>
       </c>
-      <c r="F4" s="5" t="inlineStr">
+      <c r="G4" s="5" t="inlineStr">
         <is>
           <t>60.00</t>
         </is>
       </c>
-      <c r="G4" s="5" t="inlineStr">
+      <c r="H4" s="5" t="inlineStr">
         <is>
           <t>30.00</t>
         </is>
       </c>
-      <c r="H4" s="5" t="inlineStr"/>
-      <c r="I4" s="5" t="inlineStr">
+      <c r="I4" s="5" t="inlineStr"/>
+      <c r="J4" s="5" t="inlineStr">
         <is>
           <t>150.00</t>
         </is>
@@ -1715,98 +1550,53 @@
           <t>示例-JP-WIP2</t>
         </is>
       </c>
-      <c r="B5" s="5" t="inlineStr">
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>1200</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
         <is>
           <t>2500.00</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="D5" s="5" t="inlineStr">
         <is>
           <t>80.00</t>
         </is>
       </c>
-      <c r="D5" s="5" t="inlineStr">
+      <c r="E5" s="5" t="inlineStr">
         <is>
           <t>55.00</t>
         </is>
       </c>
-      <c r="E5" s="5" t="inlineStr">
+      <c r="F5" s="5" t="inlineStr">
         <is>
           <t>40.00</t>
         </is>
       </c>
-      <c r="F5" s="5" t="inlineStr">
+      <c r="G5" s="5" t="inlineStr">
         <is>
           <t>45.00</t>
         </is>
       </c>
-      <c r="G5" s="5" t="inlineStr">
+      <c r="H5" s="5" t="inlineStr">
         <is>
           <t>25.00</t>
         </is>
       </c>
-      <c r="H5" s="5" t="inlineStr"/>
-      <c r="I5" s="5" t="inlineStr">
+      <c r="I5" s="5" t="inlineStr"/>
+      <c r="J5" s="5" t="inlineStr">
         <is>
           <t>130.00</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr"/>
-      <c r="B6" t="inlineStr"/>
-      <c r="C6" t="inlineStr"/>
-      <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr"/>
-      <c r="B7" t="inlineStr"/>
-      <c r="C7" t="inlineStr"/>
-      <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr"/>
-      <c r="B8" t="inlineStr"/>
-      <c r="C8" t="inlineStr"/>
-      <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr"/>
-      <c r="B9" t="inlineStr"/>
-      <c r="C9" t="inlineStr"/>
-      <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr"/>
-      <c r="B10" t="inlineStr"/>
-      <c r="C10" t="inlineStr"/>
-      <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr"/>
-    </row>
+    <row r="6"/>
+    <row r="7"/>
+    <row r="8"/>
+    <row r="9"/>
+    <row r="10"/>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:I1"/>
